--- a/GroßerPreis_blanko.xlsx
+++ b/GroßerPreis_blanko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc1a9add5913b3ba/Privat/GitHub/GrosserPreis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:3_{1908758B-531A-854F-AD1A-E01F8F5F60DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F484D43-2A13-9741-A870-864C68D42885}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_964D83B0AAE5E73AB1CB199D41853A1FB9324DE0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27460" yWindow="600" windowWidth="27460" windowHeight="18480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>Kategorien</t>
   </si>
@@ -47,109 +47,12 @@
     <t>Action Spiele</t>
   </si>
   <si>
-    <t>Joker</t>
-  </si>
-  <si>
-    <t>Wer war der erste König Israels? 
-Bonuspunkte: Wer war die Nachfolger? (10 weitere Punkte für jeden weiteren direkten Nachfolger)</t>
-  </si>
-  <si>
-    <t>Welcher ist der höchste Berg der Welt?</t>
-  </si>
-  <si>
-    <t>Welches Säugetier kann am längsten ohne Wasser auskommen?</t>
-  </si>
-  <si>
-    <t>Wie viele Knochen hat ein erwachsener Mensch?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KurzSpiel</t>
-  </si>
-  <si>
-    <t>Wie heißt das Gebet, das Jesus seine Jünger lehrte?</t>
-  </si>
-  <si>
-    <t>Wie hieß der Ort, an dem Mose die 10 Gebote erhielt?
-Bonus: Nenne alle Gebote die dir einfallen (5 Punkte/ Gebot; wichtigstes Gebot gibt 30 Punkte)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wer malte die Mona Lisa? </t>
-  </si>
-  <si>
-    <t>Welcher Fluss ist der längste der Welt?</t>
-  </si>
-  <si>
-    <t>Welches Tier ist das schnellste an Land?</t>
-  </si>
-  <si>
-    <t>Wie viele Liter Wasser sollte ein Mensch durchschnittlich am Tag trinken?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liegestützbattle
-</t>
-  </si>
-  <si>
-    <t>Welches Wunder vollbrachte Jesus bei der Hochzeit zu Kana?</t>
-  </si>
-  <si>
-    <t>Wie viele Tage schuf Gott die Welt?</t>
-  </si>
-  <si>
-    <t>Was ist das größte Land der Welt?</t>
-  </si>
-  <si>
-    <t>Welcher Vogel hat die größte Flügelspannweite?</t>
-  </si>
-  <si>
-    <t>Wie viele Tage hat ein Schaltjahr? (Joker)</t>
-  </si>
-  <si>
-    <t>Ballonwettrennen</t>
-  </si>
-  <si>
-    <t>Wie viele Jünger hatte Jesus? 
-Bonus: (10 Punkte/ Jünger)</t>
-  </si>
-  <si>
-    <t>Welcher Prophet wurde von einem großen Fisch verschluckt?</t>
-  </si>
-  <si>
-    <t>Welcher Planet ist der Erde am nächsten?</t>
-  </si>
-  <si>
-    <t>Welcher Kontinent ist der größte?</t>
-  </si>
-  <si>
-    <t>Welches Tier kann am höchsten springen?</t>
-  </si>
-  <si>
-    <t>Wie viele Planeten hat 
-unser Sonnensystem?</t>
-  </si>
-  <si>
-    <t>Wo wurde Jesus geboren?</t>
-  </si>
-  <si>
-    <t>Wer baute eine Arche, um die Tiere vor der Flut zu retten?</t>
-  </si>
-  <si>
-    <t>Wie viele Finger hat ein Mensch an einer Hand?</t>
-  </si>
-  <si>
-    <t>Was ist die Hauptstadt von Deutschland?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welches Tier ist das größte an Land lebende Säugetier? </t>
-  </si>
-  <si>
-    <t>Wie viele Zähne hat ein Erwachsener normalerweise?</t>
-  </si>
-  <si>
-    <t>Montagsmaler</t>
-  </si>
-  <si>
-    <t>Saul
-David, Salomo</t>
+    <t>Joker-Feld</t>
+  </si>
+  <si>
+    <t>1. Saul (erster König)
+2. David (Nachfolger)
+3. Salomo (Nachfolger)</t>
   </si>
   <si>
     <t>Mount Everest</t>
@@ -158,7 +61,7 @@
     <t>Kamel</t>
   </si>
   <si>
-    <t>206</t>
+    <t>Zielwert: 206</t>
   </si>
   <si>
     <t>Reise nach 
@@ -168,17 +71,17 @@
     <t>Vaterunser</t>
   </si>
   <si>
-    <t>Berg Sinai
-    Du sollst keine anderen Götter neben mir haben.
-    Du sollst dir kein Bildnis noch irgendein Gleichnis machen.
-    Du sollst den Namen des Herrn, deines Gottes, nicht missbrauchen.
-    Gedenke des Sabbattages, dass du ihn heiligst.
-    Du sollst deinen Vater und deine Mutter ehren.
-    Du sollst nicht töten.
-    Du sollst nicht ehebrechen.
-    Du sollst nicht stehlen.
-    Du sollst nicht falsch Zeugnis reden.
-    Du sollst nicht begehren deines Nächsten Haus.</t>
+    <t>1. Ort: Berg Sinai
+2. 1. Gebot: Keine anderen Götter
+3. 2. Gebot: Kein Bildnis machen
+4. 3. Gebot: Gottes Namen nicht missbrauchen
+5. 4. Gebot: Sabbat heiligen
+6. 5. Gebot: Eltern ehren
+7. 6. Gebot: Nicht töten
+8. 7. Gebot: Nicht ehebrechen
+9. 8. Gebot: Nicht stehlen
+10. 9. Gebot: Nicht falsch zeugen
+11. 10. Gebot: Nichts begehren des Nächsten</t>
   </si>
   <si>
     <t>Leonardo da Vinci; Joker: Louvre</t>
@@ -190,7 +93,7 @@
     <t>Gepard</t>
   </si>
   <si>
-    <t>ca. 2 Liter</t>
+    <t>Zielwert: 2</t>
   </si>
   <si>
     <t>Aus jedem Team
@@ -210,16 +113,23 @@
     <t>Wanderalbatros</t>
   </si>
   <si>
-    <t>366; Joker: Alle 4 Jahre</t>
-  </si>
-  <si>
     <t>Staffellauf mit Luftballon 
 zwischen den Beinen
 Wenn er runterfällt von neuem starten</t>
   </si>
   <si>
-    <t>12
-Simon Petrus, Andreas, Jakobus, Johannes, Philippus, Bartholomäus, Matthäus, Thomas, Jakobus, Simon, Judas, Judas Iskariot</t>
+    <t>1. Simon Petrus
+2. Andreas
+3. Jakobus
+4. Johannes
+5. Philippus
+6. Bartholomäus
+7. Matthäus
+8. Thomas
+9. Jakobus (Sohn des Alphäus)
+10. Thaddäus
+11. Simon Kananäus
+12. Judas Iskariot</t>
   </si>
   <si>
     <t>Jona</t>
@@ -228,12 +138,18 @@
     <t>Venus</t>
   </si>
   <si>
-    <t>Asien</t>
+    <t>A) Afrika
+B) Asien [KORREKT]
+C) Nordamerika
+D) Europa</t>
   </si>
   <si>
     <t>Puma</t>
   </si>
   <si>
+    <t>Zielwert: 8</t>
+  </si>
+  <si>
     <t>Bethlehem</t>
   </si>
   <si>
@@ -244,11 +160,112 @@
   </si>
   <si>
     <t>Afrikanischer Elefant</t>
+  </si>
+  <si>
+    <t>Zielwert: 32</t>
   </si>
   <si>
     <t>Einer aus der Gruppe bekommt 
 Begriffe,
 der Rest muss raten</t>
+  </si>
+  <si>
+    <t>Joker!</t>
+  </si>
+  <si>
+    <t>Wer war der erste König Israels? 
+Bonuspunkte: Wer war die Nachfolger? (10 weitere Punkte für jeden weiteren direkten Nachfolger)</t>
+  </si>
+  <si>
+    <t>Welcher ist der höchste Berg der Welt?</t>
+  </si>
+  <si>
+    <t>Welches Säugetier kann am längsten ohne Wasser auskommen?</t>
+  </si>
+  <si>
+    <t>Wie viele Knochen hat ein erwachsener Mensch?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KurzSpiel</t>
+  </si>
+  <si>
+    <t>Wie heißt das Gebet, das Jesus seine Jünger lehrte?</t>
+  </si>
+  <si>
+    <t>Wie hieß der Ort, an dem Mose die 10 Gebote erhielt?
+Bonus: Nenne alle Gebote die dir einfallen (5 Punkte/ Gebot; wichtigstes Gebot gibt 30 Punkte)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wer malte die Mona Lisa? </t>
+  </si>
+  <si>
+    <t>Welcher Fluss ist der längste der Welt?</t>
+  </si>
+  <si>
+    <t>Welches Tier ist das schnellste an Land?</t>
+  </si>
+  <si>
+    <t>Wie viele Liter Wasser sollte ein Mensch durchschnittlich am Tag trinken?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liegestützbattle
+</t>
+  </si>
+  <si>
+    <t>Welches Wunder vollbrachte Jesus bei der Hochzeit zu Kana?</t>
+  </si>
+  <si>
+    <t>Wie viele Tage schuf Gott die Welt?</t>
+  </si>
+  <si>
+    <t>Was ist das größte Land der Welt?</t>
+  </si>
+  <si>
+    <t>Welcher Vogel hat die größte Flügelspannweite?</t>
+  </si>
+  <si>
+    <t>Ballonwettrennen</t>
+  </si>
+  <si>
+    <t>Wie viele Jünger hatte Jesus? 
+Bonus: (10 Punkte/ Jünger)</t>
+  </si>
+  <si>
+    <t>Welcher Prophet wurde von einem großen Fisch verschluckt?</t>
+  </si>
+  <si>
+    <t>Welcher Planet ist der Erde am nächsten?</t>
+  </si>
+  <si>
+    <t>Welcher Kontinent ist der größte?</t>
+  </si>
+  <si>
+    <t>Welches Tier kann am höchsten springen?</t>
+  </si>
+  <si>
+    <t>Wie viele Planeten hat 
+unser Sonnensystem?</t>
+  </si>
+  <si>
+    <t>Wo wurde Jesus geboren?</t>
+  </si>
+  <si>
+    <t>Wer baute eine Arche, um die Tiere vor der Flut zu retten?</t>
+  </si>
+  <si>
+    <t>Wie viele Finger hat ein Mensch an einer Hand?</t>
+  </si>
+  <si>
+    <t>Was ist die Hauptstadt von Deutschland?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welches Tier ist das größte an Land lebende Säugetier? </t>
+  </si>
+  <si>
+    <t>Wie viele Zähne hat ein Erwachsener normalerweise?</t>
+  </si>
+  <si>
+    <t>Montagsmaler</t>
   </si>
 </sst>
 </file>
@@ -324,13 +341,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -343,16 +360,41 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
+  <dxfs count="25">
+    <dxf>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -362,27 +404,18 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -392,7 +425,126 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="31"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="31"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="31"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -401,8 +553,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -422,8 +574,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -443,8 +595,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -464,8 +616,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -485,8 +637,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -506,8 +658,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -518,57 +670,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -578,8 +679,8 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -589,31 +690,31 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -623,142 +724,26 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="31"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="31"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="31"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -775,34 +760,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B3300FE9-7CEF-E043-9A97-B3F7DEC9EBEA}" name="Tabelle1" displayName="Tabelle1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:H6" xr:uid="{B3300FE9-7CEF-E043-9A97-B3F7DEC9EBEA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{E72011DC-5629-6E46-9F20-AF33B3CC392C}" name="Kategorien" dataDxfId="14"/>
-    <tableColumn id="1" xr3:uid="{63585075-B9DA-CC4E-B131-BA2E48536DF1}" name="Bibelwissen Jesus" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{F6A8BF3D-6E83-0E48-8B01-CC5A19C064A6}" name="Bibelwissen Altes Testament" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{2029ABC4-331D-454B-98DE-B1790D50059F}" name="Allgemeinwissen" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{5002E9A7-7E1D-EA4B-986F-3AAF73E85C5F}" name="Geographie" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{E110CC1F-D00B-8F4D-9D01-B57222C47DAA}" name="Tierrekorde" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{1D3CF6C1-8982-CB43-9D5D-41157BC35BD4}" name="Schätzfragen" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{88014905-B545-B142-AF76-2428BB8FC8CA}" name="Action Spiele" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Kategorien" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Bibelwissen Jesus" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bibelwissen Altes Testament" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Allgemeinwissen" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Geographie" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tierrekorde" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Schätzfragen" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Action Spiele" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{170DBE96-44D1-5642-B7C7-AA23FC6A8C29}" name="Tabelle2" displayName="Tabelle2" ref="A1:H6" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="11">
-  <autoFilter ref="A1:H6" xr:uid="{170DBE96-44D1-5642-B7C7-AA23FC6A8C29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle2" displayName="Tabelle2" ref="A1:H6" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{18BEA581-26A5-404B-AFF6-1EE2B2C8F7B8}" name="Kategorien" dataDxfId="0"/>
-    <tableColumn id="1" xr3:uid="{9C128232-B2FD-D84E-9078-814D1C7D2E0A}" name="Bibelwissen Jesus" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{76AB29D7-FA61-1B4F-ABDA-9E9017746947}" name="Bibelwissen Altes Testament" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{B42244D1-EB96-6A44-A8EC-D13B259A6C42}" name="Allgemeinwissen" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{9A1E9917-04DA-5C4C-8E21-8C5E1772A315}" name="Geographie" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{03E6E51C-FFBF-5F4C-A6DB-ED1B600B4C9D}" name="Tierrekorde" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{38627DF9-71C1-C74C-91D4-EE35EEB2F7D6}" name="Schätzfragen" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{607E4828-7B2B-7B42-92E8-259344FD9D30}" name="Action Spiele" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Kategorien" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Bibelwissen Jesus" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Bibelwissen Altes Testament" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Allgemeinwissen" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Geographie" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tierrekorde" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Schätzfragen" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Action Spiele" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1100,7 +1085,7 @@
     <col min="2" max="8" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1131,25 +1116,25 @@
         <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
@@ -1157,25 +1142,25 @@
         <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
@@ -1183,25 +1168,25 @@
         <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
@@ -1209,25 +1194,25 @@
         <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
@@ -1235,25 +1220,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1308,22 +1293,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
@@ -1331,25 +1316,25 @@
         <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
@@ -1357,25 +1342,25 @@
         <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
@@ -1383,22 +1368,22 @@
         <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="1">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -1409,25 +1394,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="1">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/GroßerPreis_blanko.xlsx
+++ b/GroßerPreis_blanko.xlsx
@@ -1,289 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc1a9add5913b3ba/Privat/GitHub/GrosserPreis/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_964D83B0AAE5E73AB1CB199D41853A1FB9324DE0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27460" yWindow="600" windowWidth="27460" windowHeight="18480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-27460" yWindow="600" windowWidth="27460" windowHeight="18480" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fragen" sheetId="1" r:id="rId1"/>
-    <sheet name="Antworten" sheetId="2" r:id="rId2"/>
+    <sheet name="Fragen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antworten" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
-  <si>
-    <t>Kategorien</t>
-  </si>
-  <si>
-    <t>Bibelwissen Jesus</t>
-  </si>
-  <si>
-    <t>Bibelwissen Altes Testament</t>
-  </si>
-  <si>
-    <t>Allgemeinwissen</t>
-  </si>
-  <si>
-    <t>Geographie</t>
-  </si>
-  <si>
-    <t>Tierrekorde</t>
-  </si>
-  <si>
-    <t>Schätzfragen</t>
-  </si>
-  <si>
-    <t>Action Spiele</t>
-  </si>
-  <si>
-    <t>Joker-Feld</t>
-  </si>
-  <si>
-    <t>1. Saul (erster König)
-2. David (Nachfolger)
-3. Salomo (Nachfolger)</t>
-  </si>
-  <si>
-    <t>Mount Everest</t>
-  </si>
-  <si>
-    <t>Kamel</t>
-  </si>
-  <si>
-    <t>Zielwert: 206</t>
-  </si>
-  <si>
-    <t>Reise nach 
-Jerusalem</t>
-  </si>
-  <si>
-    <t>Vaterunser</t>
-  </si>
-  <si>
-    <t>1. Ort: Berg Sinai
-2. 1. Gebot: Keine anderen Götter
-3. 2. Gebot: Kein Bildnis machen
-4. 3. Gebot: Gottes Namen nicht missbrauchen
-5. 4. Gebot: Sabbat heiligen
-6. 5. Gebot: Eltern ehren
-7. 6. Gebot: Nicht töten
-8. 7. Gebot: Nicht ehebrechen
-9. 8. Gebot: Nicht stehlen
-10. 9. Gebot: Nicht falsch zeugen
-11. 10. Gebot: Nichts begehren des Nächsten</t>
-  </si>
-  <si>
-    <t>Leonardo da Vinci; Joker: Louvre</t>
-  </si>
-  <si>
-    <t>Nil</t>
-  </si>
-  <si>
-    <t>Gepard</t>
-  </si>
-  <si>
-    <t>Zielwert: 2</t>
-  </si>
-  <si>
-    <t>Aus jedem Team
-eine Person, wer nicht
-mehr kann scheidet aus</t>
-  </si>
-  <si>
-    <t>Wasser zu Wein</t>
-  </si>
-  <si>
-    <t>6 Tage, am 7. Tag ruhte er</t>
-  </si>
-  <si>
-    <t>Russland</t>
-  </si>
-  <si>
-    <t>Wanderalbatros</t>
-  </si>
-  <si>
-    <t>Staffellauf mit Luftballon 
-zwischen den Beinen
-Wenn er runterfällt von neuem starten</t>
-  </si>
-  <si>
-    <t>1. Simon Petrus
-2. Andreas
-3. Jakobus
-4. Johannes
-5. Philippus
-6. Bartholomäus
-7. Matthäus
-8. Thomas
-9. Jakobus (Sohn des Alphäus)
-10. Thaddäus
-11. Simon Kananäus
-12. Judas Iskariot</t>
-  </si>
-  <si>
-    <t>Jona</t>
-  </si>
-  <si>
-    <t>Venus</t>
-  </si>
-  <si>
-    <t>A) Afrika
-B) Asien [KORREKT]
-C) Nordamerika
-D) Europa</t>
-  </si>
-  <si>
-    <t>Puma</t>
-  </si>
-  <si>
-    <t>Zielwert: 8</t>
-  </si>
-  <si>
-    <t>Bethlehem</t>
-  </si>
-  <si>
-    <t>Noah</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>Afrikanischer Elefant</t>
-  </si>
-  <si>
-    <t>Zielwert: 32</t>
-  </si>
-  <si>
-    <t>Einer aus der Gruppe bekommt 
-Begriffe,
-der Rest muss raten</t>
-  </si>
-  <si>
-    <t>Joker!</t>
-  </si>
-  <si>
-    <t>Wer war der erste König Israels? 
-Bonuspunkte: Wer war die Nachfolger? (10 weitere Punkte für jeden weiteren direkten Nachfolger)</t>
-  </si>
-  <si>
-    <t>Welcher ist der höchste Berg der Welt?</t>
-  </si>
-  <si>
-    <t>Welches Säugetier kann am längsten ohne Wasser auskommen?</t>
-  </si>
-  <si>
-    <t>Wie viele Knochen hat ein erwachsener Mensch?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KurzSpiel</t>
-  </si>
-  <si>
-    <t>Wie heißt das Gebet, das Jesus seine Jünger lehrte?</t>
-  </si>
-  <si>
-    <t>Wie hieß der Ort, an dem Mose die 10 Gebote erhielt?
-Bonus: Nenne alle Gebote die dir einfallen (5 Punkte/ Gebot; wichtigstes Gebot gibt 30 Punkte)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wer malte die Mona Lisa? </t>
-  </si>
-  <si>
-    <t>Welcher Fluss ist der längste der Welt?</t>
-  </si>
-  <si>
-    <t>Welches Tier ist das schnellste an Land?</t>
-  </si>
-  <si>
-    <t>Wie viele Liter Wasser sollte ein Mensch durchschnittlich am Tag trinken?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liegestützbattle
-</t>
-  </si>
-  <si>
-    <t>Welches Wunder vollbrachte Jesus bei der Hochzeit zu Kana?</t>
-  </si>
-  <si>
-    <t>Wie viele Tage schuf Gott die Welt?</t>
-  </si>
-  <si>
-    <t>Was ist das größte Land der Welt?</t>
-  </si>
-  <si>
-    <t>Welcher Vogel hat die größte Flügelspannweite?</t>
-  </si>
-  <si>
-    <t>Ballonwettrennen</t>
-  </si>
-  <si>
-    <t>Wie viele Jünger hatte Jesus? 
-Bonus: (10 Punkte/ Jünger)</t>
-  </si>
-  <si>
-    <t>Welcher Prophet wurde von einem großen Fisch verschluckt?</t>
-  </si>
-  <si>
-    <t>Welcher Planet ist der Erde am nächsten?</t>
-  </si>
-  <si>
-    <t>Welcher Kontinent ist der größte?</t>
-  </si>
-  <si>
-    <t>Welches Tier kann am höchsten springen?</t>
-  </si>
-  <si>
-    <t>Wie viele Planeten hat 
-unser Sonnensystem?</t>
-  </si>
-  <si>
-    <t>Wo wurde Jesus geboren?</t>
-  </si>
-  <si>
-    <t>Wer baute eine Arche, um die Tiere vor der Flut zu retten?</t>
-  </si>
-  <si>
-    <t>Wie viele Finger hat ein Mensch an einer Hand?</t>
-  </si>
-  <si>
-    <t>Was ist die Hauptstadt von Deutschland?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welches Tier ist das größte an Land lebende Säugetier? </t>
-  </si>
-  <si>
-    <t>Wie viele Zähne hat ein Erwachsener normalerweise?</t>
-  </si>
-  <si>
-    <t>Montagsmaler</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -331,29 +76,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -748,46 +493,106 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:H6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:H6"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Kategorien" dataDxfId="7"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Bibelwissen Jesus" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bibelwissen Altes Testament" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Allgemeinwissen" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Geographie" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tierrekorde" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Schätzfragen" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Action Spiele" dataDxfId="0"/>
+    <tableColumn id="8" name="Kategorien" dataDxfId="7"/>
+    <tableColumn id="1" name="Bibelwissen Jesus" dataDxfId="6"/>
+    <tableColumn id="2" name="Bibelwissen Altes Testament" dataDxfId="5"/>
+    <tableColumn id="3" name="Allgemeinwissen" dataDxfId="4"/>
+    <tableColumn id="4" name="Geographie" dataDxfId="3"/>
+    <tableColumn id="5" name="Tierrekorde" dataDxfId="2"/>
+    <tableColumn id="6" name="Schätzfragen" dataDxfId="1"/>
+    <tableColumn id="7" name="Action Spiele" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle2" displayName="Tabelle2" ref="A1:H6" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:H6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabelle2" displayName="Tabelle2" ref="A1:H6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:H6"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Kategorien" dataDxfId="19"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Bibelwissen Jesus" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Bibelwissen Altes Testament" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Allgemeinwissen" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Geographie" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tierrekorde" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Schätzfragen" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Action Spiele" dataDxfId="12"/>
+    <tableColumn id="8" name="Kategorien" dataDxfId="19"/>
+    <tableColumn id="1" name="Bibelwissen Jesus" dataDxfId="18"/>
+    <tableColumn id="2" name="Bibelwissen Altes Testament" dataDxfId="17"/>
+    <tableColumn id="3" name="Allgemeinwissen" dataDxfId="16"/>
+    <tableColumn id="4" name="Geographie" dataDxfId="15"/>
+    <tableColumn id="5" name="Tierrekorde" dataDxfId="14"/>
+    <tableColumn id="6" name="Schätzfragen" dataDxfId="13"/>
+    <tableColumn id="7" name="Action Spiele" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1077,349 +882,565 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" customWidth="1"/>
-    <col min="2" max="8" width="23.1640625" customWidth="1"/>
+    <col width="18.1640625" customWidth="1" min="1" max="1"/>
+    <col width="23.1640625" customWidth="1" min="2" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Punkte</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Bibelwissen Jesus</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Bibelwissen Altes Testament</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Allgemeinwissen</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Geographie</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Tierrekorde</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Schätzfragen</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Action Spiele</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+    <row r="2" ht="81" customHeight="1">
+      <c r="A2" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Joker!</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Wer war der erste König Israels? 
+Bonuspunkte: Wer war die Nachfolger? (10 weitere Punkte für jeden weiteren direkten Nachfolger)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Joker!</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Welcher ist der höchste Berg der Welt?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Welches Säugetier kann am längsten ohne Wasser auskommen?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Knochen hat ein erwachsener Mensch?</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> KurzSpiel</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Wie heißt das Gebet, das Jesus seine Jünger lehrte?</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Wie hieß der Ort, an dem Mose die 10 Gebote erhielt?
+Bonus: Nenne alle Gebote die dir einfallen (5 Punkte/ Gebot; wichtigstes Gebot gibt 30 Punkte)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wer malte die Mona Lisa? </t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Welcher Fluss ist der längste der Welt?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Welches Tier ist das schnellste an Land?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Liter Wasser sollte ein Mensch durchschnittlich am Tag trinken?</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liegestützbattle
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Welches Wunder vollbrachte Jesus bei der Hochzeit zu Kana?</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Tage schuf Gott die Welt?</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Was ist das größte Land der Welt?</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Joker!</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Welcher Vogel hat die größte Flügelspannweite?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Joker!</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Ballonwettrennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="81" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Jünger hatte Jesus? 
+Bonus: (10 Punkte/ Jünger)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Welcher Prophet wurde von einem großen Fisch verschluckt?</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Welcher Planet ist der Erde am nächsten?</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Welcher Kontinent ist der größte?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Welches Tier kann am höchsten springen?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Planeten hat 
+unser Sonnensystem?</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Joker!</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>80</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>60</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>40</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+    <row r="6" ht="81" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>68</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Wo wurde Jesus geboren?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Wer baute eine Arche, um die Tiere vor der Flut zu retten?</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Finger hat ein Mensch an einer Hand?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Was ist die Hauptstadt von Deutschland?</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welches Tier ist das größte an Land lebende Säugetier? </t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Wie viele Zähne hat ein Erwachsener normalerweise?</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Montagsmaler</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="9" width="25" customWidth="1"/>
+    <col width="18.5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
+    <row r="1" ht="80" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Punkte</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Bibelwissen Jesus</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Bibelwissen Altes Testament</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Allgemeinwissen</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Geographie</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Tierrekorde</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Schätzfragen</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Action Spiele</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Joker-Feld</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>1. Saul (erster König)
+2. David (Nachfolger)
+3. Salomo (Nachfolger)</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Joker-Feld</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Mount Everest</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Kamel</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Zielwert: 206</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Reise nach 
+Jerusalem</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Vaterunser</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>1. Ort: Berg Sinai
+2. 1. Gebot: Keine anderen Götter
+3. 2. Gebot: Kein Bildnis machen
+4. 3. Gebot: Gottes Namen nicht missbrauchen
+5. 4. Gebot: Sabbat heiligen
+6. 5. Gebot: Eltern ehren
+7. 6. Gebot: Nicht töten
+8. 7. Gebot: Nicht ehebrechen
+9. 8. Gebot: Nicht stehlen
+10. 9. Gebot: Nicht falsch zeugen
+11. 10. Gebot: Nichts begehren des Nächsten</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Leonardo da Vinci; Joker: Louvre</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Gepard</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Zielwert: 2</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Aus jedem Team
+eine Person, wer nicht
+mehr kann scheidet aus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Wasser zu Wein</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>6 Tage, am 7. Tag ruhte er</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Joker-Feld</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Wanderalbatros</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Joker-Feld</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Staffellauf mit Luftballon 
+zwischen den Beinen
+Wenn er runterfällt von neuem starten</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>1. Simon Petrus
+2. Andreas
+3. Jakobus
+4. Johannes
+5. Philippus
+6. Bartholomäus
+7. Matthäus
+8. Thomas
+9. Jakobus (Sohn des Alphäus)
+10. Thaddäus
+11. Simon Kananäus
+12. Judas Iskariot</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Jona</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Venus</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>A) Afrika
+B) Asien [KORREKT]
+C) Nordamerika
+D) Europa</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Zielwert: 8</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Joker-Feld</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Bethlehem</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8">
-        <v>100</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
-        <v>80</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>60</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>37</v>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Afrikanischer Elefant</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Zielwert: 32</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Einer aus der Gruppe bekommt 
+Begriffe,
+der Rest muss raten</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>